--- a/datasets/hospital_records.xlsx
+++ b/datasets/hospital_records.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d4e4ffa798794d10/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/Hospital-Records-Analysis/datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A41BDCFE-E172-4106-9F23-204DD613F503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B2A445-040D-7243-B71F-BDA8A04F50F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="500" windowWidth="25380" windowHeight="16080" xr2:uid="{453117EB-1EFB-6D4D-9934-023BC6A18E9D}"/>
+    <workbookView xWindow="3420" yWindow="500" windowWidth="25380" windowHeight="16080" activeTab="1" xr2:uid="{453117EB-1EFB-6D4D-9934-023BC6A18E9D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Original" sheetId="1" r:id="rId1"/>
+    <sheet name="Data Dictionary" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6062" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6107" uniqueCount="111">
   <si>
     <t>Patient ID</t>
   </si>
@@ -307,12 +308,75 @@
   <si>
     <t>Chebet</t>
   </si>
+  <si>
+    <t>Column Name</t>
+  </si>
+  <si>
+    <t>Data Type</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>Unique identifier for each patient</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>Patient first name</t>
+  </si>
+  <si>
+    <t>Patient surname</t>
+  </si>
+  <si>
+    <t>Patient gender</t>
+  </si>
+  <si>
+    <t>Patient age</t>
+  </si>
+  <si>
+    <t>Text/Number</t>
+  </si>
+  <si>
+    <t>Patient contact information</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Hospital visit date</t>
+  </si>
+  <si>
+    <t>Patient diagnosis</t>
+  </si>
+  <si>
+    <t>Treatment provided</t>
+  </si>
+  <si>
+    <t>Assigned doctor</t>
+  </si>
+  <si>
+    <t>Department handling patient</t>
+  </si>
+  <si>
+    <t>Insurance company</t>
+  </si>
+  <si>
+    <t>Patient bill amount</t>
+  </si>
+  <si>
+    <t>Payment state</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -332,6 +396,27 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Abadi"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Abadi"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -354,11 +439,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -694,9 +782,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F911DBB-9D12-7948-995B-2BBA082DE62F}">
   <dimension ref="A1:N673"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -740,7 +828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>6892</v>
       </c>
@@ -784,7 +872,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>6413</v>
       </c>
@@ -828,7 +916,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>4073</v>
       </c>
@@ -872,7 +960,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>9754</v>
       </c>
@@ -916,7 +1004,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>6382</v>
       </c>
@@ -960,7 +1048,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>5961</v>
       </c>
@@ -1004,7 +1092,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>5661</v>
       </c>
@@ -1048,7 +1136,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>9297</v>
       </c>
@@ -1092,7 +1180,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>7884</v>
       </c>
@@ -1136,7 +1224,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>8654</v>
       </c>
@@ -1180,7 +1268,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>4921</v>
       </c>
@@ -1224,7 +1312,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>6550</v>
       </c>
@@ -1268,7 +1356,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2227</v>
       </c>
@@ -1312,7 +1400,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>9941</v>
       </c>
@@ -1356,7 +1444,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2152</v>
       </c>
@@ -1400,7 +1488,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2994</v>
       </c>
@@ -1444,7 +1532,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>9075</v>
       </c>
@@ -1488,7 +1576,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>3590</v>
       </c>
@@ -1532,7 +1620,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>4229</v>
       </c>
@@ -1576,7 +1664,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>3491</v>
       </c>
@@ -1620,7 +1708,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>1428</v>
       </c>
@@ -1664,7 +1752,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>9656</v>
       </c>
@@ -1708,7 +1796,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>4473</v>
       </c>
@@ -1752,7 +1840,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>6598</v>
       </c>
@@ -1796,7 +1884,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>1816</v>
       </c>
@@ -1840,7 +1928,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>6378</v>
       </c>
@@ -1884,7 +1972,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>4382</v>
       </c>
@@ -1928,7 +2016,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>3493</v>
       </c>
@@ -1972,7 +2060,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>6661</v>
       </c>
@@ -2016,7 +2104,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>6895</v>
       </c>
@@ -2060,7 +2148,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>5436</v>
       </c>
@@ -2104,7 +2192,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>1576</v>
       </c>
@@ -2148,7 +2236,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>1268</v>
       </c>
@@ -2192,7 +2280,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>2638</v>
       </c>
@@ -2236,7 +2324,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>8556</v>
       </c>
@@ -2280,7 +2368,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>5098</v>
       </c>
@@ -2324,7 +2412,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>3171</v>
       </c>
@@ -2368,7 +2456,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>4379</v>
       </c>
@@ -2412,7 +2500,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>2300</v>
       </c>
@@ -2456,7 +2544,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>9838</v>
       </c>
@@ -2500,7 +2588,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>4027</v>
       </c>
@@ -2544,7 +2632,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>1335</v>
       </c>
@@ -2588,7 +2676,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>5258</v>
       </c>
@@ -2632,7 +2720,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>6651</v>
       </c>
@@ -2676,7 +2764,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>3182</v>
       </c>
@@ -2720,7 +2808,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>1558</v>
       </c>
@@ -2764,7 +2852,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>2818</v>
       </c>
@@ -2808,7 +2896,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>9508</v>
       </c>
@@ -2852,7 +2940,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="50" spans="1:14">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>3869</v>
       </c>
@@ -2896,7 +2984,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>8286</v>
       </c>
@@ -2940,7 +3028,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:14">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>9078</v>
       </c>
@@ -2984,7 +3072,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:14">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>3361</v>
       </c>
@@ -3028,7 +3116,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:14">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>1135</v>
       </c>
@@ -3072,7 +3160,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:14">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>7717</v>
       </c>
@@ -3116,7 +3204,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="56" spans="1:14">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>9738</v>
       </c>
@@ -3160,7 +3248,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="57" spans="1:14">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>1832</v>
       </c>
@@ -3204,7 +3292,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>6720</v>
       </c>
@@ -3248,7 +3336,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>8247</v>
       </c>
@@ -3292,7 +3380,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>1330</v>
       </c>
@@ -3336,7 +3424,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>9392</v>
       </c>
@@ -3380,7 +3468,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>5686</v>
       </c>
@@ -3424,7 +3512,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>4334</v>
       </c>
@@ -3468,7 +3556,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>3018</v>
       </c>
@@ -3512,7 +3600,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="65" spans="1:14">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>9026</v>
       </c>
@@ -3556,7 +3644,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:14">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>6586</v>
       </c>
@@ -3600,7 +3688,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="67" spans="1:14">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>4130</v>
       </c>
@@ -3644,7 +3732,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="68" spans="1:14">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>9452</v>
       </c>
@@ -3688,7 +3776,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:14">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>4282</v>
       </c>
@@ -3732,7 +3820,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:14">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>3980</v>
       </c>
@@ -3776,7 +3864,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:14">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>8412</v>
       </c>
@@ -3820,7 +3908,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="72" spans="1:14">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>7045</v>
       </c>
@@ -3864,7 +3952,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="73" spans="1:14">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>4467</v>
       </c>
@@ -3908,7 +3996,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="74" spans="1:14">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>6662</v>
       </c>
@@ -3952,7 +4040,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="75" spans="1:14">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>1443</v>
       </c>
@@ -3996,7 +4084,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="76" spans="1:14">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>5174</v>
       </c>
@@ -4040,7 +4128,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="77" spans="1:14">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>3232</v>
       </c>
@@ -4084,7 +4172,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="78" spans="1:14">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>5254</v>
       </c>
@@ -4128,7 +4216,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:14">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>6594</v>
       </c>
@@ -4172,7 +4260,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="80" spans="1:14">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>9888</v>
       </c>
@@ -4216,7 +4304,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>2195</v>
       </c>
@@ -4260,7 +4348,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>9403</v>
       </c>
@@ -4304,7 +4392,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>4731</v>
       </c>
@@ -4348,7 +4436,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>7746</v>
       </c>
@@ -4392,7 +4480,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>9050</v>
       </c>
@@ -4436,7 +4524,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>7521</v>
       </c>
@@ -4480,7 +4568,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>7535</v>
       </c>
@@ -4524,7 +4612,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>3273</v>
       </c>
@@ -4568,7 +4656,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>8196</v>
       </c>
@@ -4612,7 +4700,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>3110</v>
       </c>
@@ -4656,7 +4744,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>1367</v>
       </c>
@@ -4700,7 +4788,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>3580</v>
       </c>
@@ -4744,7 +4832,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>2393</v>
       </c>
@@ -4788,7 +4876,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>5260</v>
       </c>
@@ -4832,7 +4920,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>4725</v>
       </c>
@@ -4876,7 +4964,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>1945</v>
       </c>
@@ -4920,7 +5008,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>8057</v>
       </c>
@@ -4964,7 +5052,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>7130</v>
       </c>
@@ -5008,7 +5096,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>8348</v>
       </c>
@@ -5052,7 +5140,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>8281</v>
       </c>
@@ -5096,7 +5184,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>8677</v>
       </c>
@@ -5140,7 +5228,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>3325</v>
       </c>
@@ -5184,7 +5272,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="103" spans="1:14">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>5868</v>
       </c>
@@ -5228,7 +5316,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>5696</v>
       </c>
@@ -5272,7 +5360,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="105" spans="1:14">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>5649</v>
       </c>
@@ -5316,7 +5404,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="106" spans="1:14">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>6022</v>
       </c>
@@ -5360,7 +5448,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="107" spans="1:14">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>4086</v>
       </c>
@@ -5404,7 +5492,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="108" spans="1:14">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>4239</v>
       </c>
@@ -5448,7 +5536,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="109" spans="1:14">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>2264</v>
       </c>
@@ -5492,7 +5580,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="110" spans="1:14">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>5871</v>
       </c>
@@ -5536,7 +5624,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="111" spans="1:14">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>6179</v>
       </c>
@@ -5580,7 +5668,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="112" spans="1:14">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>1459</v>
       </c>
@@ -5624,7 +5712,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="113" spans="1:14">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>2136</v>
       </c>
@@ -5668,7 +5756,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="114" spans="1:14">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>5047</v>
       </c>
@@ -5712,7 +5800,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="115" spans="1:14">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>1699</v>
       </c>
@@ -5756,7 +5844,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="116" spans="1:14">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>5067</v>
       </c>
@@ -5800,7 +5888,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="117" spans="1:14">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <v>1022</v>
       </c>
@@ -5844,7 +5932,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="118" spans="1:14">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <v>8502</v>
       </c>
@@ -5888,7 +5976,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="119" spans="1:14">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <v>6208</v>
       </c>
@@ -5932,7 +6020,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="120" spans="1:14">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
         <v>3902</v>
       </c>
@@ -5976,7 +6064,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="121" spans="1:14">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
         <v>1902</v>
       </c>
@@ -6020,7 +6108,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="122" spans="1:14">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
         <v>1767</v>
       </c>
@@ -6064,7 +6152,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="123" spans="1:14">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
         <v>7870</v>
       </c>
@@ -6108,7 +6196,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="124" spans="1:14">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
         <v>1809</v>
       </c>
@@ -6152,7 +6240,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="125" spans="1:14">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
         <v>8125</v>
       </c>
@@ -6196,7 +6284,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="126" spans="1:14">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
         <v>7625</v>
       </c>
@@ -6240,7 +6328,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="127" spans="1:14">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
         <v>1940</v>
       </c>
@@ -6284,7 +6372,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="128" spans="1:14">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
         <v>6017</v>
       </c>
@@ -6328,7 +6416,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="129" spans="1:14">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
         <v>1798</v>
       </c>
@@ -6372,7 +6460,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="130" spans="1:14">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
         <v>2315</v>
       </c>
@@ -6416,7 +6504,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="131" spans="1:14">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
         <v>6663</v>
       </c>
@@ -6460,7 +6548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="132" spans="1:14">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
         <v>7549</v>
       </c>
@@ -6504,7 +6592,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="133" spans="1:14">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
         <v>5136</v>
       </c>
@@ -6548,7 +6636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="134" spans="1:14">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
         <v>7570</v>
       </c>
@@ -6592,7 +6680,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="135" spans="1:14">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
         <v>1215</v>
       </c>
@@ -6636,7 +6724,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="136" spans="1:14">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
         <v>7189</v>
       </c>
@@ -6680,7 +6768,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="137" spans="1:14">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
         <v>6362</v>
       </c>
@@ -6724,7 +6812,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="138" spans="1:14">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
         <v>4298</v>
       </c>
@@ -6768,7 +6856,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="139" spans="1:14">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
         <v>8337</v>
       </c>
@@ -6812,7 +6900,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="140" spans="1:14">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
         <v>6365</v>
       </c>
@@ -6856,7 +6944,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="141" spans="1:14">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
         <v>9071</v>
       </c>
@@ -6900,7 +6988,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="142" spans="1:14">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
         <v>9179</v>
       </c>
@@ -6944,7 +7032,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="143" spans="1:14">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
         <v>9259</v>
       </c>
@@ -6988,7 +7076,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="144" spans="1:14">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
         <v>5943</v>
       </c>
@@ -7032,7 +7120,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="145" spans="1:14">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
         <v>1804</v>
       </c>
@@ -7076,7 +7164,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="146" spans="1:14">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
         <v>6346</v>
       </c>
@@ -7120,7 +7208,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="147" spans="1:14">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
         <v>5946</v>
       </c>
@@ -7164,7 +7252,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="148" spans="1:14">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
         <v>4931</v>
       </c>
@@ -7208,7 +7296,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="149" spans="1:14">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
         <v>4858</v>
       </c>
@@ -7252,7 +7340,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="150" spans="1:14">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
         <v>3996</v>
       </c>
@@ -7296,7 +7384,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="151" spans="1:14">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
         <v>9579</v>
       </c>
@@ -7340,7 +7428,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="152" spans="1:14">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
         <v>8793</v>
       </c>
@@ -7384,7 +7472,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="153" spans="1:14">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
         <v>8046</v>
       </c>
@@ -7428,7 +7516,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="154" spans="1:14">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
         <v>1254</v>
       </c>
@@ -7472,7 +7560,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="155" spans="1:14">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
         <v>1882</v>
       </c>
@@ -7516,7 +7604,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="156" spans="1:14">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
         <v>7922</v>
       </c>
@@ -7560,7 +7648,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="157" spans="1:14">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
         <v>3793</v>
       </c>
@@ -7604,7 +7692,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="158" spans="1:14">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
         <v>7132</v>
       </c>
@@ -7648,7 +7736,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="159" spans="1:14">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A159" s="2">
         <v>2950</v>
       </c>
@@ -7692,7 +7780,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="160" spans="1:14">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
         <v>1678</v>
       </c>
@@ -7736,7 +7824,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="161" spans="1:14">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A161" s="2">
         <v>6916</v>
       </c>
@@ -7780,7 +7868,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="162" spans="1:14">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A162" s="2">
         <v>4017</v>
       </c>
@@ -7824,7 +7912,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="163" spans="1:14">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
         <v>9896</v>
       </c>
@@ -7868,7 +7956,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="164" spans="1:14">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
         <v>3064</v>
       </c>
@@ -7912,7 +8000,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="165" spans="1:14">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A165" s="2">
         <v>5703</v>
       </c>
@@ -7956,7 +8044,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="166" spans="1:14">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A166" s="2">
         <v>2334</v>
       </c>
@@ -8000,7 +8088,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="167" spans="1:14">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A167" s="2">
         <v>8447</v>
       </c>
@@ -8044,7 +8132,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="168" spans="1:14">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A168" s="2">
         <v>5176</v>
       </c>
@@ -8088,7 +8176,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="169" spans="1:14">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A169" s="2">
         <v>6398</v>
       </c>
@@ -8132,7 +8220,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="170" spans="1:14">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A170" s="2">
         <v>3215</v>
       </c>
@@ -8176,7 +8264,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="171" spans="1:14">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A171" s="2">
         <v>9388</v>
       </c>
@@ -8220,7 +8308,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="172" spans="1:14">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A172" s="2">
         <v>9373</v>
       </c>
@@ -8264,7 +8352,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="173" spans="1:14">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A173" s="2">
         <v>8299</v>
       </c>
@@ -8308,7 +8396,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="174" spans="1:14">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A174" s="2">
         <v>4943</v>
       </c>
@@ -8352,7 +8440,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="175" spans="1:14">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A175" s="2">
         <v>3407</v>
       </c>
@@ -8396,7 +8484,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="176" spans="1:14">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A176" s="2">
         <v>2178</v>
       </c>
@@ -8440,7 +8528,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="177" spans="1:14">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A177" s="2">
         <v>8604</v>
       </c>
@@ -8484,7 +8572,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="178" spans="1:14">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A178" s="2">
         <v>8179</v>
       </c>
@@ -8528,7 +8616,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="179" spans="1:14">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A179" s="2">
         <v>7131</v>
       </c>
@@ -8572,7 +8660,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="180" spans="1:14">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A180" s="2">
         <v>3638</v>
       </c>
@@ -8616,7 +8704,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="181" spans="1:14">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A181" s="2">
         <v>3445</v>
       </c>
@@ -8660,7 +8748,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="182" spans="1:14">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A182" s="2">
         <v>5199</v>
       </c>
@@ -8704,7 +8792,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="183" spans="1:14">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A183" s="2">
         <v>2618</v>
       </c>
@@ -8748,7 +8836,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="184" spans="1:14">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A184" s="2">
         <v>6694</v>
       </c>
@@ -8792,7 +8880,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="185" spans="1:14">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A185" s="2">
         <v>4515</v>
       </c>
@@ -8836,7 +8924,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="186" spans="1:14">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A186" s="2">
         <v>4306</v>
       </c>
@@ -8880,7 +8968,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="187" spans="1:14">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A187" s="2">
         <v>3562</v>
       </c>
@@ -8924,7 +9012,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="188" spans="1:14">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A188" s="2">
         <v>2789</v>
       </c>
@@ -8968,7 +9056,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="189" spans="1:14">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A189" s="2">
         <v>7985</v>
       </c>
@@ -9012,7 +9100,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="190" spans="1:14">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A190" s="2">
         <v>8326</v>
       </c>
@@ -9056,7 +9144,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="191" spans="1:14">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A191" s="2">
         <v>6989</v>
       </c>
@@ -9100,7 +9188,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="192" spans="1:14">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A192" s="2">
         <v>6784</v>
       </c>
@@ -9144,7 +9232,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="193" spans="1:14">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A193" s="2">
         <v>9963</v>
       </c>
@@ -9188,7 +9276,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="194" spans="1:14">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A194" s="2">
         <v>4174</v>
       </c>
@@ -9232,7 +9320,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="195" spans="1:14">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A195" s="2">
         <v>5505</v>
       </c>
@@ -9276,7 +9364,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="196" spans="1:14">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A196" s="2">
         <v>9208</v>
       </c>
@@ -9320,7 +9408,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="197" spans="1:14">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A197" s="2">
         <v>3600</v>
       </c>
@@ -9364,7 +9452,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="198" spans="1:14">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A198" s="2">
         <v>6606</v>
       </c>
@@ -9408,7 +9496,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="199" spans="1:14">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A199" s="2">
         <v>7725</v>
       </c>
@@ -9452,7 +9540,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="200" spans="1:14">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A200" s="2">
         <v>7537</v>
       </c>
@@ -9496,7 +9584,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="201" spans="1:14">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A201" s="2">
         <v>7297</v>
       </c>
@@ -9540,7 +9628,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="202" spans="1:14">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A202" s="2">
         <v>1968</v>
       </c>
@@ -9584,7 +9672,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="203" spans="1:14">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A203" s="2">
         <v>6360</v>
       </c>
@@ -9628,7 +9716,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="204" spans="1:14">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A204" s="2">
         <v>8421</v>
       </c>
@@ -9672,7 +9760,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="205" spans="1:14">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A205" s="2">
         <v>9013</v>
       </c>
@@ -9716,7 +9804,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="206" spans="1:14">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A206" s="2">
         <v>9460</v>
       </c>
@@ -9760,7 +9848,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="207" spans="1:14">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A207" s="2">
         <v>1621</v>
       </c>
@@ -9804,7 +9892,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="208" spans="1:14">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A208" s="2">
         <v>3031</v>
       </c>
@@ -9848,7 +9936,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="209" spans="1:14">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A209" s="2">
         <v>2478</v>
       </c>
@@ -9892,7 +9980,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="210" spans="1:14">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A210" s="2">
         <v>6868</v>
       </c>
@@ -9936,7 +10024,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="211" spans="1:14">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A211" s="2">
         <v>2586</v>
       </c>
@@ -9980,7 +10068,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="212" spans="1:14">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A212" s="2">
         <v>1811</v>
       </c>
@@ -10024,7 +10112,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="213" spans="1:14">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A213" s="2">
         <v>3474</v>
       </c>
@@ -10068,7 +10156,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="214" spans="1:14">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A214" s="2">
         <v>8169</v>
       </c>
@@ -10112,7 +10200,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="215" spans="1:14">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A215" s="2">
         <v>7201</v>
       </c>
@@ -10156,7 +10244,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="216" spans="1:14">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A216" s="2">
         <v>5992</v>
       </c>
@@ -10200,7 +10288,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="217" spans="1:14">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A217" s="2">
         <v>7876</v>
       </c>
@@ -10244,7 +10332,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="218" spans="1:14">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A218" s="2">
         <v>1651</v>
       </c>
@@ -10288,7 +10376,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="219" spans="1:14">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A219" s="2">
         <v>3809</v>
       </c>
@@ -10332,7 +10420,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="220" spans="1:14">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A220" s="2">
         <v>4655</v>
       </c>
@@ -10376,7 +10464,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="221" spans="1:14">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A221" s="2">
         <v>2302</v>
       </c>
@@ -10420,7 +10508,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="222" spans="1:14">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A222" s="2">
         <v>3142</v>
       </c>
@@ -10464,7 +10552,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="223" spans="1:14">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A223" s="2">
         <v>9637</v>
       </c>
@@ -10508,7 +10596,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="224" spans="1:14">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A224" s="2">
         <v>7450</v>
       </c>
@@ -10552,7 +10640,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="225" spans="1:14">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A225" s="2">
         <v>9743</v>
       </c>
@@ -10596,7 +10684,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="226" spans="1:14">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A226" s="2">
         <v>2506</v>
       </c>
@@ -10640,7 +10728,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="227" spans="1:14">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A227" s="2">
         <v>7864</v>
       </c>
@@ -10684,7 +10772,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="228" spans="1:14">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A228" s="2">
         <v>8452</v>
       </c>
@@ -10728,7 +10816,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="229" spans="1:14">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A229" s="2">
         <v>3949</v>
       </c>
@@ -10772,7 +10860,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="230" spans="1:14">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A230" s="2">
         <v>9689</v>
       </c>
@@ -10816,7 +10904,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="231" spans="1:14">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A231" s="2">
         <v>8327</v>
       </c>
@@ -10860,7 +10948,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="232" spans="1:14">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A232" s="2">
         <v>4997</v>
       </c>
@@ -10904,7 +10992,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="233" spans="1:14">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A233" s="2">
         <v>1589</v>
       </c>
@@ -10948,7 +11036,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="234" spans="1:14">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A234" s="2">
         <v>7219</v>
       </c>
@@ -10992,7 +11080,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="235" spans="1:14">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A235" s="2">
         <v>1541</v>
       </c>
@@ -11036,7 +11124,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="236" spans="1:14">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A236" s="2">
         <v>8581</v>
       </c>
@@ -11080,7 +11168,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="237" spans="1:14">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A237" s="2">
         <v>5251</v>
       </c>
@@ -11124,7 +11212,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="238" spans="1:14">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A238" s="2">
         <v>2887</v>
       </c>
@@ -11168,7 +11256,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="239" spans="1:14">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A239" s="2">
         <v>3687</v>
       </c>
@@ -11212,7 +11300,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="240" spans="1:14">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A240" s="2">
         <v>2579</v>
       </c>
@@ -11256,7 +11344,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="241" spans="1:14">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A241" s="2">
         <v>3576</v>
       </c>
@@ -11300,7 +11388,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="242" spans="1:14">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A242" s="2">
         <v>3268</v>
       </c>
@@ -11344,7 +11432,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="243" spans="1:14">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A243" s="2">
         <v>7047</v>
       </c>
@@ -11388,7 +11476,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="244" spans="1:14">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A244" s="2">
         <v>2514</v>
       </c>
@@ -11432,7 +11520,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="245" spans="1:14">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A245" s="2">
         <v>8587</v>
       </c>
@@ -11476,7 +11564,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="246" spans="1:14">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A246" s="2">
         <v>6195</v>
       </c>
@@ -11520,7 +11608,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="247" spans="1:14">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A247" s="2">
         <v>9405</v>
       </c>
@@ -11564,7 +11652,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="248" spans="1:14">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A248" s="2">
         <v>2704</v>
       </c>
@@ -11608,7 +11696,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="249" spans="1:14">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A249" s="2">
         <v>4712</v>
       </c>
@@ -11652,7 +11740,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="250" spans="1:14">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A250" s="2">
         <v>3128</v>
       </c>
@@ -11696,7 +11784,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="251" spans="1:14">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A251" s="2">
         <v>8918</v>
       </c>
@@ -11740,7 +11828,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="252" spans="1:14">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A252" s="2">
         <v>9991</v>
       </c>
@@ -11784,7 +11872,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="253" spans="1:14">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A253" s="2">
         <v>6253</v>
       </c>
@@ -11828,7 +11916,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="254" spans="1:14">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A254" s="2">
         <v>5139</v>
       </c>
@@ -11872,7 +11960,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="255" spans="1:14">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A255" s="2">
         <v>3137</v>
       </c>
@@ -11916,7 +12004,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="256" spans="1:14">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A256" s="2">
         <v>9604</v>
       </c>
@@ -11960,7 +12048,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="257" spans="1:14">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A257" s="2">
         <v>9858</v>
       </c>
@@ -12004,7 +12092,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="258" spans="1:14">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A258" s="2">
         <v>1857</v>
       </c>
@@ -12048,7 +12136,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="259" spans="1:14">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A259" s="2">
         <v>7740</v>
       </c>
@@ -12092,7 +12180,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="260" spans="1:14">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A260" s="2">
         <v>3725</v>
       </c>
@@ -12136,7 +12224,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="261" spans="1:14">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A261" s="2">
         <v>2599</v>
       </c>
@@ -12180,7 +12268,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="262" spans="1:14">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A262" s="2">
         <v>1578</v>
       </c>
@@ -12224,7 +12312,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="263" spans="1:14">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A263" s="2">
         <v>4536</v>
       </c>
@@ -12268,7 +12356,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="264" spans="1:14">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A264" s="2">
         <v>3179</v>
       </c>
@@ -12312,7 +12400,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="265" spans="1:14">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A265" s="2">
         <v>3606</v>
       </c>
@@ -12356,7 +12444,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="266" spans="1:14">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A266" s="2">
         <v>3637</v>
       </c>
@@ -12400,7 +12488,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="267" spans="1:14">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A267" s="2">
         <v>5004</v>
       </c>
@@ -12444,7 +12532,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="268" spans="1:14">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A268" s="2">
         <v>7252</v>
       </c>
@@ -12488,7 +12576,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="269" spans="1:14">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A269" s="2">
         <v>9772</v>
       </c>
@@ -12532,7 +12620,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="270" spans="1:14">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A270" s="2">
         <v>7368</v>
       </c>
@@ -12576,7 +12664,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="271" spans="1:14">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A271" s="2">
         <v>8029</v>
       </c>
@@ -12620,7 +12708,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="272" spans="1:14">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A272" s="2">
         <v>9155</v>
       </c>
@@ -12664,7 +12752,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="273" spans="1:14">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A273" s="2">
         <v>4793</v>
       </c>
@@ -12708,7 +12796,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="274" spans="1:14">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A274" s="2">
         <v>8686</v>
       </c>
@@ -12752,7 +12840,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="275" spans="1:14">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A275" s="2">
         <v>5018</v>
       </c>
@@ -12796,7 +12884,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="276" spans="1:14">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A276" s="2">
         <v>4256</v>
       </c>
@@ -12840,7 +12928,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="277" spans="1:14">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A277" s="2">
         <v>8809</v>
       </c>
@@ -12884,7 +12972,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="278" spans="1:14">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A278" s="2">
         <v>3705</v>
       </c>
@@ -12928,7 +13016,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="279" spans="1:14">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A279" s="2">
         <v>1759</v>
       </c>
@@ -12972,7 +13060,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="280" spans="1:14">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A280" s="2">
         <v>4641</v>
       </c>
@@ -13016,7 +13104,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="281" spans="1:14">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A281" s="2">
         <v>2710</v>
       </c>
@@ -13060,7 +13148,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="282" spans="1:14">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A282" s="2">
         <v>6745</v>
       </c>
@@ -13104,7 +13192,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="283" spans="1:14">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A283" s="2">
         <v>2199</v>
       </c>
@@ -13148,7 +13236,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="284" spans="1:14">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A284" s="2">
         <v>9304</v>
       </c>
@@ -13192,7 +13280,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="285" spans="1:14">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A285" s="2">
         <v>7343</v>
       </c>
@@ -13236,7 +13324,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="286" spans="1:14">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A286" s="2">
         <v>7161</v>
       </c>
@@ -13280,7 +13368,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="287" spans="1:14">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A287" s="2">
         <v>8504</v>
       </c>
@@ -13324,7 +13412,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="288" spans="1:14">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A288" s="2">
         <v>3239</v>
       </c>
@@ -13368,7 +13456,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="289" spans="1:14">
+    <row r="289" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A289" s="2">
         <v>5396</v>
       </c>
@@ -13412,7 +13500,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="290" spans="1:14">
+    <row r="290" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A290" s="2">
         <v>1730</v>
       </c>
@@ -13456,7 +13544,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="291" spans="1:14">
+    <row r="291" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A291" s="2">
         <v>4185</v>
       </c>
@@ -13500,7 +13588,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="292" spans="1:14">
+    <row r="292" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A292" s="2">
         <v>5404</v>
       </c>
@@ -13544,7 +13632,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="293" spans="1:14">
+    <row r="293" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A293" s="2">
         <v>2702</v>
       </c>
@@ -13588,7 +13676,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="294" spans="1:14">
+    <row r="294" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A294" s="2">
         <v>4819</v>
       </c>
@@ -13632,7 +13720,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="295" spans="1:14">
+    <row r="295" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A295" s="2">
         <v>9353</v>
       </c>
@@ -13676,7 +13764,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="296" spans="1:14">
+    <row r="296" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A296" s="2">
         <v>7509</v>
       </c>
@@ -13720,7 +13808,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="297" spans="1:14">
+    <row r="297" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A297" s="2">
         <v>5751</v>
       </c>
@@ -13764,7 +13852,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="298" spans="1:14">
+    <row r="298" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A298" s="2">
         <v>2471</v>
       </c>
@@ -13808,7 +13896,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="299" spans="1:14">
+    <row r="299" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A299" s="2">
         <v>2991</v>
       </c>
@@ -13852,7 +13940,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="300" spans="1:14">
+    <row r="300" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A300" s="2">
         <v>8255</v>
       </c>
@@ -13896,7 +13984,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="301" spans="1:14">
+    <row r="301" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A301" s="2">
         <v>2611</v>
       </c>
@@ -13940,7 +14028,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="302" spans="1:14">
+    <row r="302" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A302" s="2">
         <v>6950</v>
       </c>
@@ -13984,7 +14072,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="303" spans="1:14">
+    <row r="303" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A303" s="2">
         <v>4355</v>
       </c>
@@ -14028,7 +14116,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="304" spans="1:14">
+    <row r="304" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A304" s="2">
         <v>7507</v>
       </c>
@@ -14072,7 +14160,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="305" spans="1:14">
+    <row r="305" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A305" s="2">
         <v>4910</v>
       </c>
@@ -14116,7 +14204,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="306" spans="1:14">
+    <row r="306" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A306" s="2">
         <v>5882</v>
       </c>
@@ -14160,7 +14248,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="307" spans="1:14">
+    <row r="307" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A307" s="2">
         <v>6630</v>
       </c>
@@ -14204,7 +14292,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="308" spans="1:14">
+    <row r="308" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A308" s="2">
         <v>6666</v>
       </c>
@@ -14248,7 +14336,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="309" spans="1:14">
+    <row r="309" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A309" s="2">
         <v>1378</v>
       </c>
@@ -14292,7 +14380,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="310" spans="1:14">
+    <row r="310" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A310" s="2">
         <v>1871</v>
       </c>
@@ -14336,7 +14424,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="311" spans="1:14">
+    <row r="311" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A311" s="2">
         <v>7305</v>
       </c>
@@ -14380,7 +14468,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="312" spans="1:14">
+    <row r="312" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A312" s="2">
         <v>8533</v>
       </c>
@@ -14424,7 +14512,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="313" spans="1:14">
+    <row r="313" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A313" s="2">
         <v>2002</v>
       </c>
@@ -14468,7 +14556,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="314" spans="1:14">
+    <row r="314" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A314" s="2">
         <v>3601</v>
       </c>
@@ -14512,7 +14600,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="315" spans="1:14">
+    <row r="315" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A315" s="2">
         <v>5918</v>
       </c>
@@ -14556,7 +14644,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="316" spans="1:14">
+    <row r="316" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A316" s="2">
         <v>1331</v>
       </c>
@@ -14600,7 +14688,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="317" spans="1:14">
+    <row r="317" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A317" s="2">
         <v>8997</v>
       </c>
@@ -14644,7 +14732,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="318" spans="1:14">
+    <row r="318" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A318" s="2">
         <v>7362</v>
       </c>
@@ -14688,7 +14776,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="319" spans="1:14">
+    <row r="319" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A319" s="2">
         <v>4014</v>
       </c>
@@ -14732,7 +14820,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="320" spans="1:14">
+    <row r="320" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A320" s="2">
         <v>1309</v>
       </c>
@@ -14776,7 +14864,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="321" spans="1:14">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A321" s="2">
         <v>9067</v>
       </c>
@@ -14820,7 +14908,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="322" spans="1:14">
+    <row r="322" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A322" s="2">
         <v>7906</v>
       </c>
@@ -14864,7 +14952,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="323" spans="1:14">
+    <row r="323" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A323" s="2">
         <v>1301</v>
       </c>
@@ -14908,7 +14996,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="324" spans="1:14">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A324" s="2">
         <v>2155</v>
       </c>
@@ -14952,7 +15040,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="325" spans="1:14">
+    <row r="325" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A325" s="2">
         <v>1093</v>
       </c>
@@ -14996,7 +15084,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="326" spans="1:14">
+    <row r="326" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A326" s="2">
         <v>7300</v>
       </c>
@@ -15040,7 +15128,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="327" spans="1:14">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A327" s="2">
         <v>8511</v>
       </c>
@@ -15084,7 +15172,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="328" spans="1:14">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A328" s="2">
         <v>9556</v>
       </c>
@@ -15128,7 +15216,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="329" spans="1:14">
+    <row r="329" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A329" s="2">
         <v>3314</v>
       </c>
@@ -15172,7 +15260,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="330" spans="1:14">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A330" s="2">
         <v>5597</v>
       </c>
@@ -15216,7 +15304,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="331" spans="1:14">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A331" s="2">
         <v>9988</v>
       </c>
@@ -15260,7 +15348,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="332" spans="1:14">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A332" s="2">
         <v>6217</v>
       </c>
@@ -15304,7 +15392,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="333" spans="1:14">
+    <row r="333" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A333" s="2">
         <v>8019</v>
       </c>
@@ -15348,7 +15436,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="334" spans="1:14">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A334" s="2">
         <v>8090</v>
       </c>
@@ -15392,7 +15480,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="335" spans="1:14">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A335" s="2">
         <v>9509</v>
       </c>
@@ -15436,7 +15524,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="336" spans="1:14">
+    <row r="336" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A336" s="2">
         <v>2695</v>
       </c>
@@ -15480,7 +15568,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="337" spans="1:14">
+    <row r="337" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A337" s="2">
         <v>8290</v>
       </c>
@@ -15524,7 +15612,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="338" spans="1:14">
+    <row r="338" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A338" s="2">
         <v>9771</v>
       </c>
@@ -15568,7 +15656,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="339" spans="1:14">
+    <row r="339" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A339" s="2">
         <v>2891</v>
       </c>
@@ -15612,7 +15700,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="340" spans="1:14">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A340" s="2">
         <v>8128</v>
       </c>
@@ -15656,7 +15744,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="341" spans="1:14">
+    <row r="341" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A341" s="2">
         <v>8965</v>
       </c>
@@ -15700,7 +15788,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="342" spans="1:14">
+    <row r="342" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A342" s="2">
         <v>7945</v>
       </c>
@@ -15744,7 +15832,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="343" spans="1:14">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A343" s="2">
         <v>2968</v>
       </c>
@@ -15788,7 +15876,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="344" spans="1:14">
+    <row r="344" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A344" s="2">
         <v>3312</v>
       </c>
@@ -15832,7 +15920,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="345" spans="1:14">
+    <row r="345" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A345" s="2">
         <v>7032</v>
       </c>
@@ -15876,7 +15964,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="346" spans="1:14">
+    <row r="346" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A346" s="2">
         <v>5310</v>
       </c>
@@ -15920,7 +16008,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="347" spans="1:14">
+    <row r="347" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A347" s="2">
         <v>4501</v>
       </c>
@@ -15964,7 +16052,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="348" spans="1:14">
+    <row r="348" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A348" s="2">
         <v>7358</v>
       </c>
@@ -16008,7 +16096,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="349" spans="1:14">
+    <row r="349" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A349" s="2">
         <v>4245</v>
       </c>
@@ -16052,7 +16140,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="350" spans="1:14">
+    <row r="350" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A350" s="2">
         <v>2218</v>
       </c>
@@ -16096,7 +16184,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="351" spans="1:14">
+    <row r="351" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A351" s="2">
         <v>1665</v>
       </c>
@@ -16140,7 +16228,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="352" spans="1:14">
+    <row r="352" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A352" s="2">
         <v>1210</v>
       </c>
@@ -16184,7 +16272,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="353" spans="1:14">
+    <row r="353" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A353" s="2">
         <v>9542</v>
       </c>
@@ -16228,7 +16316,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="354" spans="1:14">
+    <row r="354" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A354" s="2">
         <v>5736</v>
       </c>
@@ -16272,7 +16360,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="355" spans="1:14">
+    <row r="355" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A355" s="2">
         <v>4216</v>
       </c>
@@ -16316,7 +16404,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="356" spans="1:14">
+    <row r="356" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A356" s="2">
         <v>1303</v>
       </c>
@@ -16360,7 +16448,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="357" spans="1:14">
+    <row r="357" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A357" s="2">
         <v>7402</v>
       </c>
@@ -16404,7 +16492,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="358" spans="1:14">
+    <row r="358" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A358" s="2">
         <v>7185</v>
       </c>
@@ -16448,7 +16536,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="359" spans="1:14">
+    <row r="359" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A359" s="2">
         <v>9846</v>
       </c>
@@ -16492,7 +16580,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="360" spans="1:14">
+    <row r="360" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A360" s="2">
         <v>5182</v>
       </c>
@@ -16536,7 +16624,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="361" spans="1:14">
+    <row r="361" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A361" s="2">
         <v>9497</v>
       </c>
@@ -16580,7 +16668,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="362" spans="1:14">
+    <row r="362" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A362" s="2">
         <v>3415</v>
       </c>
@@ -16624,7 +16712,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="363" spans="1:14">
+    <row r="363" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A363" s="2">
         <v>3926</v>
       </c>
@@ -16668,7 +16756,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="364" spans="1:14">
+    <row r="364" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A364" s="2">
         <v>6635</v>
       </c>
@@ -16712,7 +16800,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="365" spans="1:14">
+    <row r="365" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A365" s="2">
         <v>2817</v>
       </c>
@@ -16756,7 +16844,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="366" spans="1:14">
+    <row r="366" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A366" s="2">
         <v>3478</v>
       </c>
@@ -16800,7 +16888,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="367" spans="1:14">
+    <row r="367" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A367" s="2">
         <v>5503</v>
       </c>
@@ -16844,7 +16932,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="368" spans="1:14">
+    <row r="368" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A368" s="2">
         <v>3420</v>
       </c>
@@ -16888,7 +16976,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="369" spans="1:14">
+    <row r="369" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A369" s="2">
         <v>1875</v>
       </c>
@@ -16932,7 +17020,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="370" spans="1:14">
+    <row r="370" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A370" s="2">
         <v>4752</v>
       </c>
@@ -16976,7 +17064,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="371" spans="1:14">
+    <row r="371" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A371" s="2">
         <v>6625</v>
       </c>
@@ -17020,7 +17108,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="372" spans="1:14">
+    <row r="372" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A372" s="2">
         <v>3246</v>
       </c>
@@ -17064,7 +17152,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="373" spans="1:14">
+    <row r="373" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A373" s="2">
         <v>5759</v>
       </c>
@@ -17108,7 +17196,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="374" spans="1:14">
+    <row r="374" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A374" s="2">
         <v>5401</v>
       </c>
@@ -17152,7 +17240,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="375" spans="1:14">
+    <row r="375" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A375" s="2">
         <v>9101</v>
       </c>
@@ -17196,7 +17284,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="376" spans="1:14">
+    <row r="376" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A376" s="2">
         <v>6973</v>
       </c>
@@ -17240,7 +17328,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="377" spans="1:14">
+    <row r="377" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A377" s="2">
         <v>4673</v>
       </c>
@@ -17284,7 +17372,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="378" spans="1:14">
+    <row r="378" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A378" s="2">
         <v>2047</v>
       </c>
@@ -17328,7 +17416,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="379" spans="1:14">
+    <row r="379" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A379" s="2">
         <v>7476</v>
       </c>
@@ -17372,7 +17460,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="380" spans="1:14">
+    <row r="380" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A380" s="2">
         <v>6006</v>
       </c>
@@ -17416,7 +17504,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="381" spans="1:14">
+    <row r="381" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A381" s="2">
         <v>7530</v>
       </c>
@@ -17460,7 +17548,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="382" spans="1:14">
+    <row r="382" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A382" s="2">
         <v>3959</v>
       </c>
@@ -17504,7 +17592,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="383" spans="1:14">
+    <row r="383" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A383" s="2">
         <v>9732</v>
       </c>
@@ -17548,7 +17636,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="384" spans="1:14">
+    <row r="384" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A384" s="2">
         <v>7016</v>
       </c>
@@ -17592,7 +17680,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="385" spans="1:14">
+    <row r="385" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A385" s="2">
         <v>9770</v>
       </c>
@@ -17636,7 +17724,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="386" spans="1:14">
+    <row r="386" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A386" s="2">
         <v>9647</v>
       </c>
@@ -17680,7 +17768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="387" spans="1:14">
+    <row r="387" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A387" s="2">
         <v>8075</v>
       </c>
@@ -17724,7 +17812,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="388" spans="1:14">
+    <row r="388" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A388" s="2">
         <v>1464</v>
       </c>
@@ -17768,7 +17856,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="389" spans="1:14">
+    <row r="389" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A389" s="2">
         <v>5952</v>
       </c>
@@ -17812,7 +17900,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="390" spans="1:14">
+    <row r="390" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A390" s="2">
         <v>1916</v>
       </c>
@@ -17856,7 +17944,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="391" spans="1:14">
+    <row r="391" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A391" s="2">
         <v>5195</v>
       </c>
@@ -17900,7 +17988,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="392" spans="1:14">
+    <row r="392" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A392" s="2">
         <v>1248</v>
       </c>
@@ -17944,7 +18032,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="393" spans="1:14">
+    <row r="393" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A393" s="2">
         <v>6473</v>
       </c>
@@ -17988,7 +18076,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="394" spans="1:14">
+    <row r="394" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A394" s="2">
         <v>3517</v>
       </c>
@@ -18032,7 +18120,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="395" spans="1:14">
+    <row r="395" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A395" s="2">
         <v>8958</v>
       </c>
@@ -18076,7 +18164,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="396" spans="1:14">
+    <row r="396" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A396" s="2">
         <v>5410</v>
       </c>
@@ -18120,7 +18208,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="397" spans="1:14">
+    <row r="397" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A397" s="2">
         <v>2685</v>
       </c>
@@ -18164,7 +18252,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="398" spans="1:14">
+    <row r="398" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A398" s="2">
         <v>9726</v>
       </c>
@@ -18208,7 +18296,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="399" spans="1:14">
+    <row r="399" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A399" s="2">
         <v>4836</v>
       </c>
@@ -18252,7 +18340,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="400" spans="1:14">
+    <row r="400" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A400" s="2">
         <v>7827</v>
       </c>
@@ -18296,7 +18384,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="401" spans="1:14">
+    <row r="401" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A401" s="2">
         <v>7061</v>
       </c>
@@ -18340,7 +18428,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="402" spans="1:14">
+    <row r="402" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A402" s="2">
         <v>8094</v>
       </c>
@@ -18384,7 +18472,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="403" spans="1:14">
+    <row r="403" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A403" s="2">
         <v>8262</v>
       </c>
@@ -18428,7 +18516,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="404" spans="1:14">
+    <row r="404" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A404" s="2">
         <v>5738</v>
       </c>
@@ -18472,7 +18560,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="405" spans="1:14">
+    <row r="405" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A405" s="2">
         <v>7334</v>
       </c>
@@ -18516,7 +18604,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="406" spans="1:14">
+    <row r="406" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A406" s="2">
         <v>1782</v>
       </c>
@@ -18560,7 +18648,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="407" spans="1:14">
+    <row r="407" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A407" s="2">
         <v>6949</v>
       </c>
@@ -18604,7 +18692,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="408" spans="1:14">
+    <row r="408" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A408" s="2">
         <v>3384</v>
       </c>
@@ -18648,7 +18736,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="409" spans="1:14">
+    <row r="409" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A409" s="2">
         <v>7843</v>
       </c>
@@ -18692,7 +18780,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="410" spans="1:14">
+    <row r="410" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A410" s="2">
         <v>3901</v>
       </c>
@@ -18736,7 +18824,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="411" spans="1:14">
+    <row r="411" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A411" s="2">
         <v>3090</v>
       </c>
@@ -18780,7 +18868,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="412" spans="1:14">
+    <row r="412" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A412" s="2">
         <v>6088</v>
       </c>
@@ -18824,7 +18912,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="413" spans="1:14">
+    <row r="413" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A413" s="2">
         <v>9841</v>
       </c>
@@ -18868,7 +18956,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="414" spans="1:14">
+    <row r="414" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A414" s="2">
         <v>3883</v>
       </c>
@@ -18912,7 +19000,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="415" spans="1:14">
+    <row r="415" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A415" s="2">
         <v>7809</v>
       </c>
@@ -18956,7 +19044,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="416" spans="1:14">
+    <row r="416" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A416" s="2">
         <v>6645</v>
       </c>
@@ -19000,7 +19088,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="417" spans="1:14">
+    <row r="417" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A417" s="2">
         <v>1458</v>
       </c>
@@ -19044,7 +19132,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="418" spans="1:14">
+    <row r="418" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A418" s="2">
         <v>3895</v>
       </c>
@@ -19088,7 +19176,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="419" spans="1:14">
+    <row r="419" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A419" s="2">
         <v>9653</v>
       </c>
@@ -19132,7 +19220,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="420" spans="1:14">
+    <row r="420" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A420" s="2">
         <v>3755</v>
       </c>
@@ -19176,7 +19264,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="421" spans="1:14">
+    <row r="421" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A421" s="2">
         <v>6940</v>
       </c>
@@ -19220,7 +19308,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="422" spans="1:14">
+    <row r="422" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A422" s="2">
         <v>8761</v>
       </c>
@@ -19264,7 +19352,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="423" spans="1:14">
+    <row r="423" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A423" s="2">
         <v>8900</v>
       </c>
@@ -19308,7 +19396,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="424" spans="1:14">
+    <row r="424" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A424" s="2">
         <v>6050</v>
       </c>
@@ -19352,7 +19440,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="425" spans="1:14">
+    <row r="425" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A425" s="2">
         <v>5547</v>
       </c>
@@ -19396,7 +19484,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="426" spans="1:14">
+    <row r="426" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A426" s="2">
         <v>9575</v>
       </c>
@@ -19440,7 +19528,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="427" spans="1:14">
+    <row r="427" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A427" s="2">
         <v>1278</v>
       </c>
@@ -19484,7 +19572,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="428" spans="1:14">
+    <row r="428" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A428" s="2">
         <v>3212</v>
       </c>
@@ -19528,7 +19616,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="429" spans="1:14">
+    <row r="429" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A429" s="2">
         <v>1750</v>
       </c>
@@ -19572,7 +19660,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="430" spans="1:14">
+    <row r="430" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A430" s="2">
         <v>1460</v>
       </c>
@@ -19616,7 +19704,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="431" spans="1:14">
+    <row r="431" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A431" s="2">
         <v>3094</v>
       </c>
@@ -19660,7 +19748,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="432" spans="1:14">
+    <row r="432" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A432" s="2">
         <v>5076</v>
       </c>
@@ -19704,7 +19792,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="433" spans="1:14">
+    <row r="433" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A433" s="2">
         <v>3352</v>
       </c>
@@ -19748,7 +19836,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="434" spans="1:14">
+    <row r="434" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A434" s="2">
         <v>4657</v>
       </c>
@@ -19792,7 +19880,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="435" spans="1:14">
+    <row r="435" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A435" s="2">
         <v>2118</v>
       </c>
@@ -19836,7 +19924,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="436" spans="1:14">
+    <row r="436" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A436" s="2">
         <v>3174</v>
       </c>
@@ -19880,7 +19968,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="437" spans="1:14">
+    <row r="437" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A437" s="2">
         <v>6430</v>
       </c>
@@ -19924,7 +20012,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="438" spans="1:14">
+    <row r="438" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A438" s="2">
         <v>4169</v>
       </c>
@@ -19968,7 +20056,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="439" spans="1:14">
+    <row r="439" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A439" s="2">
         <v>9074</v>
       </c>
@@ -20012,7 +20100,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="440" spans="1:14">
+    <row r="440" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A440" s="2">
         <v>2771</v>
       </c>
@@ -20056,7 +20144,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="441" spans="1:14">
+    <row r="441" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A441" s="2">
         <v>6515</v>
       </c>
@@ -20100,7 +20188,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="442" spans="1:14">
+    <row r="442" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A442" s="2">
         <v>7111</v>
       </c>
@@ -20144,7 +20232,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="443" spans="1:14">
+    <row r="443" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A443" s="2">
         <v>2384</v>
       </c>
@@ -20188,7 +20276,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="444" spans="1:14">
+    <row r="444" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A444" s="2">
         <v>1077</v>
       </c>
@@ -20232,7 +20320,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="445" spans="1:14">
+    <row r="445" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A445" s="2">
         <v>7916</v>
       </c>
@@ -20276,7 +20364,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="446" spans="1:14">
+    <row r="446" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A446" s="2">
         <v>8675</v>
       </c>
@@ -20320,7 +20408,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="447" spans="1:14">
+    <row r="447" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A447" s="2">
         <v>2258</v>
       </c>
@@ -20364,7 +20452,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="448" spans="1:14">
+    <row r="448" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A448" s="2">
         <v>6904</v>
       </c>
@@ -20408,7 +20496,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="449" spans="1:14">
+    <row r="449" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A449" s="2">
         <v>1352</v>
       </c>
@@ -20452,7 +20540,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="450" spans="1:14">
+    <row r="450" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A450" s="2">
         <v>5606</v>
       </c>
@@ -20496,7 +20584,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="451" spans="1:14">
+    <row r="451" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A451" s="2">
         <v>2368</v>
       </c>
@@ -20540,7 +20628,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="452" spans="1:14">
+    <row r="452" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A452" s="2">
         <v>8197</v>
       </c>
@@ -20584,7 +20672,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="453" spans="1:14">
+    <row r="453" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A453" s="2">
         <v>7978</v>
       </c>
@@ -20628,7 +20716,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="454" spans="1:14">
+    <row r="454" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A454" s="2">
         <v>6590</v>
       </c>
@@ -20672,7 +20760,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="455" spans="1:14">
+    <row r="455" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A455" s="2">
         <v>4895</v>
       </c>
@@ -20716,7 +20804,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="456" spans="1:14">
+    <row r="456" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A456" s="2">
         <v>9628</v>
       </c>
@@ -20760,7 +20848,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="457" spans="1:14">
+    <row r="457" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A457" s="2">
         <v>2661</v>
       </c>
@@ -20804,7 +20892,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="458" spans="1:14">
+    <row r="458" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A458" s="2">
         <v>5163</v>
       </c>
@@ -20848,7 +20936,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="459" spans="1:14">
+    <row r="459" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A459" s="2">
         <v>4881</v>
       </c>
@@ -20892,7 +20980,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="460" spans="1:14">
+    <row r="460" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A460" s="2">
         <v>6221</v>
       </c>
@@ -20936,7 +21024,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="461" spans="1:14">
+    <row r="461" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A461" s="2">
         <v>3999</v>
       </c>
@@ -20980,7 +21068,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="462" spans="1:14">
+    <row r="462" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A462" s="2">
         <v>1424</v>
       </c>
@@ -21024,7 +21112,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="463" spans="1:14">
+    <row r="463" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A463" s="2">
         <v>8234</v>
       </c>
@@ -21068,7 +21156,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="464" spans="1:14">
+    <row r="464" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A464" s="2">
         <v>2549</v>
       </c>
@@ -21112,7 +21200,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="465" spans="1:14">
+    <row r="465" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A465" s="2">
         <v>1327</v>
       </c>
@@ -21156,7 +21244,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="466" spans="1:14">
+    <row r="466" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A466" s="2">
         <v>7576</v>
       </c>
@@ -21200,7 +21288,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="467" spans="1:14">
+    <row r="467" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A467" s="2">
         <v>1770</v>
       </c>
@@ -21244,7 +21332,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="468" spans="1:14">
+    <row r="468" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A468" s="2">
         <v>7984</v>
       </c>
@@ -21288,7 +21376,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="469" spans="1:14">
+    <row r="469" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A469" s="2">
         <v>3220</v>
       </c>
@@ -21332,7 +21420,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="470" spans="1:14">
+    <row r="470" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A470" s="2">
         <v>1746</v>
       </c>
@@ -21376,7 +21464,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="471" spans="1:14">
+    <row r="471" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A471" s="2">
         <v>7033</v>
       </c>
@@ -21420,7 +21508,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="472" spans="1:14">
+    <row r="472" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A472" s="2">
         <v>7431</v>
       </c>
@@ -21464,7 +21552,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="473" spans="1:14">
+    <row r="473" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A473" s="2">
         <v>2424</v>
       </c>
@@ -21508,7 +21596,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="474" spans="1:14">
+    <row r="474" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A474" s="2">
         <v>2912</v>
       </c>
@@ -21552,7 +21640,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="475" spans="1:14">
+    <row r="475" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A475" s="2">
         <v>3550</v>
       </c>
@@ -21596,7 +21684,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="476" spans="1:14">
+    <row r="476" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A476" s="2">
         <v>7648</v>
       </c>
@@ -21640,7 +21728,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="477" spans="1:14">
+    <row r="477" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A477" s="2">
         <v>7005</v>
       </c>
@@ -21684,7 +21772,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="478" spans="1:14">
+    <row r="478" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A478" s="2">
         <v>6526</v>
       </c>
@@ -21728,7 +21816,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="479" spans="1:14">
+    <row r="479" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A479" s="2">
         <v>2285</v>
       </c>
@@ -21772,7 +21860,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="480" spans="1:14">
+    <row r="480" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A480" s="2">
         <v>4783</v>
       </c>
@@ -21816,7 +21904,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="481" spans="1:14">
+    <row r="481" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A481" s="2">
         <v>7832</v>
       </c>
@@ -21860,7 +21948,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="482" spans="1:14">
+    <row r="482" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A482" s="2">
         <v>7786</v>
       </c>
@@ -21904,7 +21992,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="483" spans="1:14">
+    <row r="483" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A483" s="2">
         <v>8384</v>
       </c>
@@ -21948,7 +22036,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="484" spans="1:14">
+    <row r="484" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A484" s="2">
         <v>4211</v>
       </c>
@@ -21992,7 +22080,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="485" spans="1:14">
+    <row r="485" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A485" s="2">
         <v>3994</v>
       </c>
@@ -22036,7 +22124,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="486" spans="1:14">
+    <row r="486" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A486" s="2">
         <v>8209</v>
       </c>
@@ -22080,7 +22168,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="487" spans="1:14">
+    <row r="487" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A487" s="2">
         <v>2941</v>
       </c>
@@ -22124,7 +22212,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="488" spans="1:14">
+    <row r="488" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A488" s="2">
         <v>8567</v>
       </c>
@@ -22168,7 +22256,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="489" spans="1:14">
+    <row r="489" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A489" s="2">
         <v>6691</v>
       </c>
@@ -22212,7 +22300,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="490" spans="1:14">
+    <row r="490" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A490" s="2">
         <v>7268</v>
       </c>
@@ -22256,7 +22344,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="491" spans="1:14">
+    <row r="491" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A491" s="2">
         <v>4716</v>
       </c>
@@ -22300,7 +22388,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="492" spans="1:14">
+    <row r="492" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A492" s="2">
         <v>4002</v>
       </c>
@@ -22344,7 +22432,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="493" spans="1:14">
+    <row r="493" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A493" s="2">
         <v>8338</v>
       </c>
@@ -22388,7 +22476,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="494" spans="1:14">
+    <row r="494" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A494" s="2">
         <v>4435</v>
       </c>
@@ -22432,7 +22520,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="495" spans="1:14">
+    <row r="495" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A495" s="2">
         <v>8052</v>
       </c>
@@ -22476,7 +22564,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="496" spans="1:14">
+    <row r="496" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A496" s="2">
         <v>3162</v>
       </c>
@@ -22520,7 +22608,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="497" spans="1:14">
+    <row r="497" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A497" s="2">
         <v>6090</v>
       </c>
@@ -22564,7 +22652,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="498" spans="1:14">
+    <row r="498" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A498" s="2">
         <v>5980</v>
       </c>
@@ -22608,7 +22696,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="499" spans="1:14">
+    <row r="499" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A499" s="2">
         <v>4404</v>
       </c>
@@ -22652,7 +22740,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="500" spans="1:14">
+    <row r="500" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A500" s="2">
         <v>5468</v>
       </c>
@@ -22696,7 +22784,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="501" spans="1:14">
+    <row r="501" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A501" s="2">
         <v>4568</v>
       </c>
@@ -22740,7 +22828,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="502" spans="1:14">
+    <row r="502" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A502" s="2">
         <v>5006</v>
       </c>
@@ -22784,7 +22872,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="503" spans="1:14">
+    <row r="503" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A503" s="2">
         <v>6209</v>
       </c>
@@ -22828,7 +22916,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="504" spans="1:14">
+    <row r="504" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A504" s="2">
         <v>2100</v>
       </c>
@@ -22872,7 +22960,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="505" spans="1:14">
+    <row r="505" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A505" s="2">
         <v>6644</v>
       </c>
@@ -22916,7 +23004,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="506" spans="1:14">
+    <row r="506" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A506" s="2">
         <v>5127</v>
       </c>
@@ -22960,7 +23048,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="507" spans="1:14">
+    <row r="507" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A507" s="2">
         <v>9525</v>
       </c>
@@ -23004,7 +23092,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="508" spans="1:14">
+    <row r="508" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A508" s="2">
         <v>8667</v>
       </c>
@@ -23048,7 +23136,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="509" spans="1:14">
+    <row r="509" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A509" s="2">
         <v>7522</v>
       </c>
@@ -23092,7 +23180,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="510" spans="1:14">
+    <row r="510" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A510" s="2">
         <v>8189</v>
       </c>
@@ -23136,7 +23224,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="511" spans="1:14">
+    <row r="511" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A511" s="2">
         <v>8974</v>
       </c>
@@ -23180,7 +23268,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="512" spans="1:14">
+    <row r="512" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A512" s="2">
         <v>3777</v>
       </c>
@@ -23224,7 +23312,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="513" spans="1:14">
+    <row r="513" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A513" s="2">
         <v>2111</v>
       </c>
@@ -23268,7 +23356,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="514" spans="1:14">
+    <row r="514" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A514" s="2">
         <v>8324</v>
       </c>
@@ -23312,7 +23400,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="515" spans="1:14">
+    <row r="515" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A515" s="2">
         <v>4289</v>
       </c>
@@ -23356,7 +23444,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="516" spans="1:14">
+    <row r="516" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A516" s="2">
         <v>5014</v>
       </c>
@@ -23400,7 +23488,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="517" spans="1:14">
+    <row r="517" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A517" s="2">
         <v>3964</v>
       </c>
@@ -23444,7 +23532,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="518" spans="1:14">
+    <row r="518" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A518" s="2">
         <v>8343</v>
       </c>
@@ -23488,7 +23576,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="519" spans="1:14">
+    <row r="519" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A519" s="2">
         <v>9528</v>
       </c>
@@ -23532,7 +23620,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="520" spans="1:14">
+    <row r="520" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A520" s="2">
         <v>2297</v>
       </c>
@@ -23576,7 +23664,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="521" spans="1:14">
+    <row r="521" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A521" s="2">
         <v>4104</v>
       </c>
@@ -23620,7 +23708,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="522" spans="1:14">
+    <row r="522" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A522" s="2">
         <v>7842</v>
       </c>
@@ -23664,7 +23752,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="523" spans="1:14">
+    <row r="523" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A523" s="2">
         <v>7595</v>
       </c>
@@ -23708,7 +23796,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="524" spans="1:14">
+    <row r="524" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A524" s="2">
         <v>5153</v>
       </c>
@@ -23752,7 +23840,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="525" spans="1:14">
+    <row r="525" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A525" s="2">
         <v>3539</v>
       </c>
@@ -23796,7 +23884,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="526" spans="1:14">
+    <row r="526" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A526" s="2">
         <v>5383</v>
       </c>
@@ -23840,7 +23928,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="527" spans="1:14">
+    <row r="527" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A527" s="2">
         <v>4476</v>
       </c>
@@ -23884,7 +23972,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="528" spans="1:14">
+    <row r="528" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A528" s="2">
         <v>1488</v>
       </c>
@@ -23928,7 +24016,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="529" spans="1:14">
+    <row r="529" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A529" s="2">
         <v>1167</v>
       </c>
@@ -23972,7 +24060,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="530" spans="1:14">
+    <row r="530" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A530" s="2">
         <v>6380</v>
       </c>
@@ -24016,7 +24104,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="531" spans="1:14">
+    <row r="531" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A531" s="2">
         <v>5753</v>
       </c>
@@ -24060,7 +24148,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="532" spans="1:14">
+    <row r="532" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A532" s="2">
         <v>7936</v>
       </c>
@@ -24104,7 +24192,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="533" spans="1:14">
+    <row r="533" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A533" s="2">
         <v>1819</v>
       </c>
@@ -24148,7 +24236,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="534" spans="1:14">
+    <row r="534" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A534" s="2">
         <v>5065</v>
       </c>
@@ -24192,7 +24280,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="535" spans="1:14">
+    <row r="535" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A535" s="2">
         <v>8407</v>
       </c>
@@ -24236,7 +24324,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="536" spans="1:14">
+    <row r="536" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A536" s="2">
         <v>1675</v>
       </c>
@@ -24280,7 +24368,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="537" spans="1:14">
+    <row r="537" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A537" s="2">
         <v>1057</v>
       </c>
@@ -24324,7 +24412,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="538" spans="1:14">
+    <row r="538" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A538" s="2">
         <v>4765</v>
       </c>
@@ -24368,7 +24456,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="539" spans="1:14">
+    <row r="539" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A539" s="2">
         <v>2114</v>
       </c>
@@ -24412,7 +24500,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="540" spans="1:14">
+    <row r="540" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A540" s="2">
         <v>8725</v>
       </c>
@@ -24456,7 +24544,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="541" spans="1:14">
+    <row r="541" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A541" s="2">
         <v>9884</v>
       </c>
@@ -24500,7 +24588,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="542" spans="1:14">
+    <row r="542" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A542" s="2">
         <v>6728</v>
       </c>
@@ -24544,7 +24632,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="543" spans="1:14">
+    <row r="543" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A543" s="2">
         <v>3265</v>
       </c>
@@ -24588,7 +24676,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="544" spans="1:14">
+    <row r="544" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A544" s="2">
         <v>9441</v>
       </c>
@@ -24632,7 +24720,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="545" spans="1:14">
+    <row r="545" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A545" s="2">
         <v>8743</v>
       </c>
@@ -24676,7 +24764,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="546" spans="1:14">
+    <row r="546" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A546" s="2">
         <v>2903</v>
       </c>
@@ -24720,7 +24808,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="547" spans="1:14">
+    <row r="547" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A547" s="2">
         <v>1919</v>
       </c>
@@ -24764,7 +24852,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="548" spans="1:14">
+    <row r="548" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A548" s="2">
         <v>8623</v>
       </c>
@@ -24808,7 +24896,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="549" spans="1:14">
+    <row r="549" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A549" s="2">
         <v>5427</v>
       </c>
@@ -24852,7 +24940,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="550" spans="1:14">
+    <row r="550" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A550" s="2">
         <v>8253</v>
       </c>
@@ -24896,7 +24984,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="551" spans="1:14">
+    <row r="551" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A551" s="2">
         <v>7285</v>
       </c>
@@ -24940,7 +25028,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="552" spans="1:14">
+    <row r="552" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A552" s="2">
         <v>8037</v>
       </c>
@@ -24984,7 +25072,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="553" spans="1:14">
+    <row r="553" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A553" s="2">
         <v>9711</v>
       </c>
@@ -25028,7 +25116,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="554" spans="1:14">
+    <row r="554" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A554" s="2">
         <v>7206</v>
       </c>
@@ -25072,7 +25160,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="555" spans="1:14">
+    <row r="555" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A555" s="2">
         <v>4118</v>
       </c>
@@ -25116,7 +25204,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="556" spans="1:14">
+    <row r="556" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A556" s="2">
         <v>4184</v>
       </c>
@@ -25160,7 +25248,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="557" spans="1:14">
+    <row r="557" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A557" s="2">
         <v>4845</v>
       </c>
@@ -25204,7 +25292,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="558" spans="1:14">
+    <row r="558" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A558" s="2">
         <v>7705</v>
       </c>
@@ -25248,7 +25336,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="559" spans="1:14">
+    <row r="559" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A559" s="2">
         <v>6602</v>
       </c>
@@ -25292,7 +25380,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="560" spans="1:14">
+    <row r="560" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A560" s="2">
         <v>5734</v>
       </c>
@@ -25336,7 +25424,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="561" spans="1:14">
+    <row r="561" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A561" s="2">
         <v>3516</v>
       </c>
@@ -25380,7 +25468,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="562" spans="1:14">
+    <row r="562" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A562" s="2">
         <v>5807</v>
       </c>
@@ -25424,7 +25512,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="563" spans="1:14">
+    <row r="563" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A563" s="2">
         <v>7550</v>
       </c>
@@ -25468,7 +25556,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="564" spans="1:14">
+    <row r="564" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A564" s="2">
         <v>8572</v>
       </c>
@@ -25512,7 +25600,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="565" spans="1:14">
+    <row r="565" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A565" s="2">
         <v>1234</v>
       </c>
@@ -25556,7 +25644,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="566" spans="1:14">
+    <row r="566" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A566" s="2">
         <v>6637</v>
       </c>
@@ -25600,7 +25688,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="567" spans="1:14">
+    <row r="567" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A567" s="2">
         <v>8887</v>
       </c>
@@ -25644,7 +25732,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="568" spans="1:14">
+    <row r="568" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A568" s="2">
         <v>5450</v>
       </c>
@@ -25688,7 +25776,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="569" spans="1:14">
+    <row r="569" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A569" s="2">
         <v>5053</v>
       </c>
@@ -25732,7 +25820,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="570" spans="1:14">
+    <row r="570" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A570" s="2">
         <v>4629</v>
       </c>
@@ -25776,7 +25864,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="571" spans="1:14">
+    <row r="571" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A571" s="2">
         <v>8436</v>
       </c>
@@ -25820,7 +25908,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="572" spans="1:14">
+    <row r="572" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A572" s="2">
         <v>8224</v>
       </c>
@@ -25864,7 +25952,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="573" spans="1:14">
+    <row r="573" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A573" s="2">
         <v>5331</v>
       </c>
@@ -25908,7 +25996,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="574" spans="1:14">
+    <row r="574" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A574" s="2">
         <v>6351</v>
       </c>
@@ -25952,7 +26040,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="575" spans="1:14">
+    <row r="575" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A575" s="2">
         <v>5442</v>
       </c>
@@ -25996,7 +26084,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="576" spans="1:14">
+    <row r="576" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A576" s="2">
         <v>5135</v>
       </c>
@@ -26040,7 +26128,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="577" spans="1:14">
+    <row r="577" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A577" s="2">
         <v>5884</v>
       </c>
@@ -26084,7 +26172,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="578" spans="1:14">
+    <row r="578" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A578" s="2">
         <v>1153</v>
       </c>
@@ -26128,7 +26216,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="579" spans="1:14">
+    <row r="579" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A579" s="2">
         <v>5896</v>
       </c>
@@ -26172,7 +26260,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="580" spans="1:14">
+    <row r="580" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A580" s="2">
         <v>7014</v>
       </c>
@@ -26216,7 +26304,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="581" spans="1:14">
+    <row r="581" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A581" s="2">
         <v>5923</v>
       </c>
@@ -26260,7 +26348,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="582" spans="1:14">
+    <row r="582" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A582" s="2">
         <v>3443</v>
       </c>
@@ -26304,7 +26392,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="583" spans="1:14">
+    <row r="583" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A583" s="2">
         <v>6405</v>
       </c>
@@ -26348,7 +26436,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="584" spans="1:14">
+    <row r="584" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A584" s="2">
         <v>5377</v>
       </c>
@@ -26392,7 +26480,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="585" spans="1:14">
+    <row r="585" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A585" s="2">
         <v>6760</v>
       </c>
@@ -26436,7 +26524,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="586" spans="1:14">
+    <row r="586" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A586" s="2">
         <v>7040</v>
       </c>
@@ -26480,7 +26568,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="587" spans="1:14">
+    <row r="587" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A587" s="2">
         <v>6783</v>
       </c>
@@ -26524,7 +26612,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="588" spans="1:14">
+    <row r="588" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A588" s="2">
         <v>9626</v>
       </c>
@@ -26568,7 +26656,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="589" spans="1:14">
+    <row r="589" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A589" s="2">
         <v>3596</v>
       </c>
@@ -26612,7 +26700,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="590" spans="1:14">
+    <row r="590" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A590" s="2">
         <v>2225</v>
       </c>
@@ -26656,7 +26744,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="591" spans="1:14">
+    <row r="591" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A591" s="2">
         <v>3172</v>
       </c>
@@ -26700,7 +26788,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="592" spans="1:14">
+    <row r="592" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A592" s="2">
         <v>9298</v>
       </c>
@@ -26744,7 +26832,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="593" spans="1:14">
+    <row r="593" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A593" s="2">
         <v>5177</v>
       </c>
@@ -26788,7 +26876,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="594" spans="1:14">
+    <row r="594" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A594" s="2">
         <v>9285</v>
       </c>
@@ -26832,7 +26920,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="595" spans="1:14">
+    <row r="595" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A595" s="2">
         <v>7706</v>
       </c>
@@ -26876,7 +26964,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="596" spans="1:14">
+    <row r="596" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A596" s="2">
         <v>6540</v>
       </c>
@@ -26920,7 +27008,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="597" spans="1:14">
+    <row r="597" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A597" s="2">
         <v>6915</v>
       </c>
@@ -26964,7 +27052,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="598" spans="1:14">
+    <row r="598" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A598" s="2">
         <v>8032</v>
       </c>
@@ -27008,7 +27096,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="599" spans="1:14">
+    <row r="599" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A599" s="2">
         <v>5382</v>
       </c>
@@ -27052,7 +27140,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="600" spans="1:14">
+    <row r="600" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A600" s="2">
         <v>7685</v>
       </c>
@@ -27096,7 +27184,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="601" spans="1:14">
+    <row r="601" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A601" s="2">
         <v>9211</v>
       </c>
@@ -27140,7 +27228,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="602" spans="1:14">
+    <row r="602" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A602" s="2">
         <v>9016</v>
       </c>
@@ -27184,7 +27272,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="603" spans="1:14">
+    <row r="603" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A603" s="2">
         <v>4939</v>
       </c>
@@ -27228,7 +27316,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="604" spans="1:14">
+    <row r="604" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A604" s="2">
         <v>7483</v>
       </c>
@@ -27272,7 +27360,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="605" spans="1:14">
+    <row r="605" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A605" s="2">
         <v>7710</v>
       </c>
@@ -27316,7 +27404,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="606" spans="1:14">
+    <row r="606" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A606" s="2">
         <v>6873</v>
       </c>
@@ -27360,7 +27448,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="607" spans="1:14">
+    <row r="607" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A607" s="2">
         <v>9468</v>
       </c>
@@ -27404,7 +27492,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="608" spans="1:14">
+    <row r="608" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A608" s="2">
         <v>1092</v>
       </c>
@@ -27448,7 +27536,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="609" spans="1:14">
+    <row r="609" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A609" s="2">
         <v>4776</v>
       </c>
@@ -27492,7 +27580,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="610" spans="1:14">
+    <row r="610" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A610" s="2">
         <v>2307</v>
       </c>
@@ -27536,7 +27624,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="611" spans="1:14">
+    <row r="611" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A611" s="2">
         <v>9046</v>
       </c>
@@ -27580,7 +27668,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="612" spans="1:14">
+    <row r="612" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A612" s="2">
         <v>4094</v>
       </c>
@@ -27624,7 +27712,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="613" spans="1:14">
+    <row r="613" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A613" s="2">
         <v>3308</v>
       </c>
@@ -27668,7 +27756,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="614" spans="1:14">
+    <row r="614" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A614" s="2">
         <v>6886</v>
       </c>
@@ -27712,7 +27800,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="615" spans="1:14">
+    <row r="615" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A615" s="2">
         <v>1566</v>
       </c>
@@ -27756,7 +27844,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="616" spans="1:14">
+    <row r="616" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A616" s="2">
         <v>7934</v>
       </c>
@@ -27800,7 +27888,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="617" spans="1:14">
+    <row r="617" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A617" s="2">
         <v>1366</v>
       </c>
@@ -27844,7 +27932,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="618" spans="1:14">
+    <row r="618" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A618" s="2">
         <v>7976</v>
       </c>
@@ -27888,7 +27976,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="619" spans="1:14">
+    <row r="619" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A619" s="2">
         <v>8044</v>
       </c>
@@ -27932,7 +28020,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="620" spans="1:14">
+    <row r="620" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A620" s="2">
         <v>4060</v>
       </c>
@@ -27976,7 +28064,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="621" spans="1:14">
+    <row r="621" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A621" s="2">
         <v>5359</v>
       </c>
@@ -28020,7 +28108,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="622" spans="1:14">
+    <row r="622" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A622" s="2">
         <v>1341</v>
       </c>
@@ -28064,7 +28152,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="623" spans="1:14">
+    <row r="623" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A623" s="2">
         <v>9112</v>
       </c>
@@ -28108,7 +28196,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="624" spans="1:14">
+    <row r="624" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A624" s="2">
         <v>3693</v>
       </c>
@@ -28152,7 +28240,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="625" spans="1:14">
+    <row r="625" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A625" s="2">
         <v>8036</v>
       </c>
@@ -28196,7 +28284,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="626" spans="1:14">
+    <row r="626" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A626" s="2">
         <v>2877</v>
       </c>
@@ -28240,7 +28328,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="627" spans="1:14">
+    <row r="627" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A627" s="2">
         <v>4595</v>
       </c>
@@ -28284,7 +28372,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="628" spans="1:14">
+    <row r="628" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A628" s="2">
         <v>6553</v>
       </c>
@@ -28328,7 +28416,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="629" spans="1:14">
+    <row r="629" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A629" s="2">
         <v>2509</v>
       </c>
@@ -28372,7 +28460,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="630" spans="1:14">
+    <row r="630" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A630" s="2">
         <v>1489</v>
       </c>
@@ -28416,7 +28504,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="631" spans="1:14">
+    <row r="631" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A631" s="2">
         <v>5233</v>
       </c>
@@ -28460,7 +28548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="632" spans="1:14">
+    <row r="632" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A632" s="2">
         <v>7658</v>
       </c>
@@ -28504,7 +28592,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="633" spans="1:14">
+    <row r="633" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A633" s="2">
         <v>8861</v>
       </c>
@@ -28548,7 +28636,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="634" spans="1:14">
+    <row r="634" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A634" s="2">
         <v>7349</v>
       </c>
@@ -28592,7 +28680,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="635" spans="1:14">
+    <row r="635" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A635" s="2">
         <v>4598</v>
       </c>
@@ -28636,7 +28724,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="636" spans="1:14">
+    <row r="636" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A636" s="2">
         <v>9548</v>
       </c>
@@ -28680,7 +28768,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="637" spans="1:14">
+    <row r="637" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A637" s="2">
         <v>1382</v>
       </c>
@@ -28724,7 +28812,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="638" spans="1:14">
+    <row r="638" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A638" s="2">
         <v>6493</v>
       </c>
@@ -28768,7 +28856,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="639" spans="1:14">
+    <row r="639" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A639" s="2">
         <v>1310</v>
       </c>
@@ -28812,7 +28900,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="640" spans="1:14">
+    <row r="640" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A640" s="2">
         <v>4117</v>
       </c>
@@ -28856,7 +28944,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="641" spans="1:14">
+    <row r="641" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A641" s="2">
         <v>4537</v>
       </c>
@@ -28900,7 +28988,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="642" spans="1:14">
+    <row r="642" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A642" s="2">
         <v>5973</v>
       </c>
@@ -28944,7 +29032,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="643" spans="1:14">
+    <row r="643" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A643" s="2">
         <v>5413</v>
       </c>
@@ -28988,7 +29076,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="644" spans="1:14">
+    <row r="644" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A644" s="2">
         <v>2184</v>
       </c>
@@ -29032,7 +29120,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="645" spans="1:14">
+    <row r="645" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A645" s="2">
         <v>1322</v>
       </c>
@@ -29076,7 +29164,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="646" spans="1:14">
+    <row r="646" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A646" s="2">
         <v>1690</v>
       </c>
@@ -29120,7 +29208,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="647" spans="1:14">
+    <row r="647" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A647" s="2">
         <v>1145</v>
       </c>
@@ -29164,7 +29252,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="648" spans="1:14">
+    <row r="648" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A648" s="2">
         <v>3865</v>
       </c>
@@ -29208,7 +29296,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="649" spans="1:14">
+    <row r="649" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A649" s="2">
         <v>8231</v>
       </c>
@@ -29252,7 +29340,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="650" spans="1:14">
+    <row r="650" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A650" s="2">
         <v>9068</v>
       </c>
@@ -29296,7 +29384,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="651" spans="1:14">
+    <row r="651" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A651" s="2">
         <v>3195</v>
       </c>
@@ -29340,7 +29428,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="652" spans="1:14">
+    <row r="652" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A652" s="2">
         <v>6018</v>
       </c>
@@ -29384,7 +29472,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="653" spans="1:14">
+    <row r="653" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A653" s="2">
         <v>5678</v>
       </c>
@@ -29428,7 +29516,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="654" spans="1:14">
+    <row r="654" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A654" s="2">
         <v>2004</v>
       </c>
@@ -29472,7 +29560,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="655" spans="1:14">
+    <row r="655" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A655" s="2">
         <v>2862</v>
       </c>
@@ -29516,7 +29604,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="656" spans="1:14">
+    <row r="656" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A656" s="2">
         <v>9451</v>
       </c>
@@ -29560,7 +29648,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="657" spans="1:14">
+    <row r="657" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A657" s="2">
         <v>2436</v>
       </c>
@@ -29604,7 +29692,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="658" spans="1:14">
+    <row r="658" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A658" s="2">
         <v>3931</v>
       </c>
@@ -29648,7 +29736,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="659" spans="1:14">
+    <row r="659" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A659" s="2">
         <v>7512</v>
       </c>
@@ -29692,7 +29780,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="660" spans="1:14">
+    <row r="660" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A660" s="2">
         <v>8360</v>
       </c>
@@ -29736,7 +29824,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="661" spans="1:14">
+    <row r="661" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A661" s="2">
         <v>1229</v>
       </c>
@@ -29780,7 +29868,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="662" spans="1:14">
+    <row r="662" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A662" s="2">
         <v>8016</v>
       </c>
@@ -29824,7 +29912,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="663" spans="1:14">
+    <row r="663" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A663" s="2">
         <v>1054</v>
       </c>
@@ -29868,7 +29956,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="664" spans="1:14">
+    <row r="664" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A664" s="2">
         <v>4171</v>
       </c>
@@ -29912,7 +30000,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="665" spans="1:14">
+    <row r="665" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A665" s="2">
         <v>1128</v>
       </c>
@@ -29956,7 +30044,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="666" spans="1:14">
+    <row r="666" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A666" s="2">
         <v>2405</v>
       </c>
@@ -30000,7 +30088,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="667" spans="1:14">
+    <row r="667" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A667" s="2">
         <v>6539</v>
       </c>
@@ -30044,7 +30132,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="668" spans="1:14">
+    <row r="668" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A668" s="2">
         <v>6522</v>
       </c>
@@ -30088,7 +30176,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="669" spans="1:14">
+    <row r="669" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A669" s="2">
         <v>3888</v>
       </c>
@@ -30132,7 +30220,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="670" spans="1:14">
+    <row r="670" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A670" s="2">
         <v>4290</v>
       </c>
@@ -30176,7 +30264,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="671" spans="1:14">
+    <row r="671" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A671" s="2">
         <v>2129</v>
       </c>
@@ -30220,7 +30308,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="672" spans="1:14">
+    <row r="672" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A672" s="2">
         <v>9903</v>
       </c>
@@ -30264,7 +30352,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="673" spans="1:14">
+    <row r="673" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A673" s="2">
         <v>6986</v>
       </c>
@@ -30306,6 +30394,186 @@
       </c>
       <c r="N673" s="2" t="s">
         <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37270DEE-E494-CA41-9D60-F1B15A13534D}">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" customWidth="1"/>
+    <col min="3" max="3" width="31.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
